--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487680_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487680_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.8412</v>
+        <v>11.2744</v>
       </c>
       <c r="E2" t="n">
-        <v>9.776400000000001</v>
+        <v>9.936999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0648</v>
+        <v>1.3374</v>
       </c>
       <c r="G2" t="n">
         <v>6.648</v>
@@ -610,13 +610,13 @@
         <v>1.7463</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0606</v>
+        <v>0.3726</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0011</v>
+        <v>0.1618</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0617</v>
+        <v>0.2109</v>
       </c>
       <c r="V2" t="n">
         <v>3.6716</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7</v>
+        <v>3.7272</v>
       </c>
       <c r="E3" t="n">
         <v>3.5142</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1858</v>
+        <v>0.2131</v>
       </c>
       <c r="G3" t="n">
         <v>5.0937</v>
@@ -688,13 +688,13 @@
         <v>1.3582</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0541</v>
+        <v>0.0813</v>
       </c>
       <c r="T3" t="n">
         <v>0.0617</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0076</v>
+        <v>0.0197</v>
       </c>
       <c r="V3" t="n">
         <v>-1.8358</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ GREGORIO</t>
+          <t>J. SAEZ BENITO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5</v>
+        <v>3.124</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8999</v>
+        <v>2.0851</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3999</v>
+        <v>1.0389</v>
       </c>
       <c r="G4" t="n">
-        <v>4.9337</v>
+        <v>0.5665</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.029</v>
+        <v>1.0999</v>
       </c>
       <c r="I4" t="n">
-        <v>5.9627</v>
+        <v>-0.5333</v>
       </c>
       <c r="J4" t="n">
-        <v>5.6029</v>
+        <v>0.6179</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.243</v>
+        <v>1.001</v>
       </c>
       <c r="L4" t="n">
-        <v>5.8459</v>
+        <v>-0.3832</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6692</v>
+        <v>-0.0513</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.786</v>
+        <v>0.0989</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1168</v>
+        <v>-0.1502</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.7463</v>
+        <v>0.9702</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.1045</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3582</v>
+        <v>0.9702</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5946</v>
+        <v>0.6455</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7896</v>
+        <v>0.2434</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1949</v>
+        <v>0.4021</v>
       </c>
       <c r="V4" t="n">
+        <v>0.9418</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.2239</v>
+      </c>
+      <c r="X4" t="n">
         <v>-0.2821</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.6119</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-0.894</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.407</v>
+        <v>3.1034</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1123</v>
+        <v>2.6724</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2947</v>
+        <v>0.431</v>
       </c>
       <c r="G5" t="n">
         <v>1.2324</v>
@@ -844,13 +844,13 @@
         <v>1.3582</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1462</v>
+        <v>0.8426</v>
       </c>
       <c r="T5" t="n">
-        <v>0.923</v>
+        <v>0.4831</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2232</v>
+        <v>0.3595</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3299</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SAEZ BENITO</t>
+          <t>S. RODRIGUEZ GREGORIO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.9816</v>
+        <v>3.0629</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0245</v>
+        <v>3.2993</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9571</v>
+        <v>-0.2364</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5665</v>
+        <v>4.9337</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0999</v>
+        <v>-1.029</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5333</v>
+        <v>5.9627</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6179</v>
+        <v>5.6029</v>
       </c>
       <c r="K6" t="n">
-        <v>1.001</v>
+        <v>-0.243</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.3832</v>
+        <v>5.8459</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0513</v>
+        <v>-0.6692</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0989</v>
+        <v>-0.786</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1502</v>
+        <v>0.1168</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9702</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.1045</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9702</v>
+        <v>1.3582</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5031</v>
+        <v>0.1576</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1828</v>
+        <v>0.189</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3203</v>
+        <v>-0.0314</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9418</v>
+        <v>-0.2821</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2239</v>
+        <v>0.6119</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2821</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.9</v>
+        <v>2.7454</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5814</v>
+        <v>2.4813</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3186</v>
+        <v>0.2641</v>
       </c>
       <c r="G7" t="n">
         <v>1.3789</v>
@@ -1000,13 +1000,13 @@
         <v>1.7463</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3271</v>
+        <v>0.1724</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1951</v>
+        <v>0.095</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1319</v>
+        <v>0.0774</v>
       </c>
       <c r="V7" t="n">
         <v>0.6119</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5576</v>
+        <v>2.2639</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5517</v>
+        <v>4.0127</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9941</v>
+        <v>-1.7488</v>
       </c>
       <c r="G8" t="n">
         <v>1.7543</v>
@@ -1078,13 +1078,13 @@
         <v>1.1642</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2728</v>
+        <v>0.4335</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2905</v>
+        <v>0.1705</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0177</v>
+        <v>0.263</v>
       </c>
       <c r="V8" t="n">
         <v>-0.894</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9416</v>
+        <v>-0.4891</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0195</v>
+        <v>0.8419</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9221</v>
+        <v>-1.331</v>
       </c>
       <c r="G9" t="n">
         <v>1.7411</v>
@@ -1156,13 +1156,13 @@
         <v>1.9403</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6472</v>
+        <v>1.0997</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6539</v>
+        <v>0.2075</v>
       </c>
       <c r="U9" t="n">
-        <v>1.3011</v>
+        <v>0.8922</v>
       </c>
       <c r="V9" t="n">
         <v>-2.1657</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3633</v>
+        <v>-2.945</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2016</v>
+        <v>-3.4018</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8384</v>
+        <v>0.4568</v>
       </c>
       <c r="G10" t="n">
         <v>-0.866</v>
@@ -1234,13 +1234,13 @@
         <v>0.9702</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1027</v>
+        <v>0.521</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3768</v>
+        <v>0.1766</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7259</v>
+        <v>0.3443</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6597</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0886</v>
+        <v>-3.0702</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.212</v>
+        <v>-0.1119</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8766</v>
+        <v>-2.9583</v>
       </c>
       <c r="G11" t="n">
         <v>2.8217</v>
@@ -1312,13 +1312,13 @@
         <v>0.9702</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3461</v>
+        <v>-0.3278</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3634</v>
+        <v>-0.2633</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0173</v>
+        <v>-0.0645</v>
       </c>
       <c r="V11" t="n">
         <v>-3.6238</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>22.4939</v>
+        <v>22.7969</v>
       </c>
       <c r="E12" t="n">
-        <v>25.0273</v>
+        <v>25.3302</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.5333</v>
+        <v>-2.5332</v>
       </c>
       <c r="G12" t="n">
         <v>25.3043</v>
       </c>
       <c r="H12" t="n">
-        <v>4.366600000000001</v>
+        <v>4.3666</v>
       </c>
       <c r="I12" t="n">
         <v>20.938</v>
@@ -1381,7 +1381,7 @@
         <v>-1.5296</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.9402</v>
+        <v>-1.940199999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-15.5226</v>
@@ -1390,16 +1390,16 @@
         <v>13.5823</v>
       </c>
       <c r="S12" t="n">
-        <v>3.695500000000001</v>
+        <v>3.9984</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2223</v>
+        <v>1.5253</v>
       </c>
       <c r="U12" t="n">
         <v>2.4732</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.565700000000001</v>
+        <v>-4.5657</v>
       </c>
       <c r="W12" t="n">
         <v>6.6357</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.8466</v>
+        <v>4.4927</v>
       </c>
       <c r="E13" t="n">
-        <v>7.1876</v>
+        <v>7.8883</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.3411</v>
+        <v>-3.3956</v>
       </c>
       <c r="G13" t="n">
         <v>1.2662</v>
@@ -1468,13 +1468,13 @@
         <v>2.7164</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6913</v>
+        <v>-0.0451</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0902</v>
+        <v>-0.3895</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3989</v>
+        <v>0.3443</v>
       </c>
       <c r="V13" t="n">
         <v>2.4955</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.5165</v>
+        <v>-1.4892</v>
       </c>
       <c r="E14" t="n">
         <v>0.1885</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.705</v>
+        <v>-1.6777</v>
       </c>
       <c r="G14" t="n">
         <v>-3.4211</v>
@@ -1546,13 +1546,13 @@
         <v>2.3284</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0177</v>
+        <v>0.0095</v>
       </c>
       <c r="T14" t="n">
         <v>-0.3017</v>
       </c>
       <c r="U14" t="n">
-        <v>0.284</v>
+        <v>0.3113</v>
       </c>
       <c r="V14" t="n">
         <v>0.5642</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.0147</v>
+        <v>-1.6049</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4168</v>
+        <v>1.0173</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.4315</v>
+        <v>-2.6222</v>
       </c>
       <c r="G15" t="n">
         <v>-2.6854</v>
@@ -1624,13 +1624,13 @@
         <v>2.7164</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6128</v>
+        <v>-0.203</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0902</v>
+        <v>-0.4896</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4774</v>
+        <v>0.2866</v>
       </c>
       <c r="V15" t="n">
         <v>2.4477</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.241</v>
+        <v>-1.7983</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6333</v>
+        <v>-0.4331</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6077</v>
+        <v>-1.3652</v>
       </c>
       <c r="G16" t="n">
         <v>-1.6228</v>
@@ -1702,13 +1702,13 @@
         <v>0.3881</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0063</v>
+        <v>-0.5636</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4116</v>
+        <v>-0.2114</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5946</v>
+        <v>-0.3522</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. LLACER SIMLAT</t>
+          <t>J. ABRIL RAMIRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.6826</v>
+        <v>-2.3452</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7983</v>
+        <v>1.6601</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.4809</v>
+        <v>-4.0053</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.6353</v>
+        <v>0.283</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1089</v>
+        <v>1.1411</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.5264</v>
+        <v>-0.8581</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1844</v>
+        <v>3.5999</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1895</v>
+        <v>2.278</v>
       </c>
       <c r="L17" t="n">
-        <v>0.005</v>
+        <v>1.3219</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.4508</v>
+        <v>-3.317</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9195</v>
+        <v>-1.137</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.5314</v>
+        <v>-2.18</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5523</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R17" t="n">
         <v>1.5523</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2115</v>
+        <v>-1.2699</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2412</v>
+        <v>-0.5353</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0296</v>
+        <v>-0.7346</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2239</v>
+        <v>1.506</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6119</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. ABRIL RAMIRO</t>
+          <t>E. LLACER SIMLAT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.9425</v>
+        <v>-2.4918</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3598</v>
+        <v>0.7983</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.3023</v>
+        <v>-3.2901</v>
       </c>
       <c r="G18" t="n">
-        <v>0.283</v>
+        <v>-4.6353</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1411</v>
+        <v>-1.1089</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8581</v>
+        <v>-3.5264</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5999</v>
+        <v>-0.1844</v>
       </c>
       <c r="K18" t="n">
-        <v>2.278</v>
+        <v>-0.1895</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3219</v>
+        <v>0.005</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.317</v>
+        <v>-4.4508</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.137</v>
+        <v>-0.9195</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.18</v>
+        <v>-3.5314</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.3582</v>
+        <v>1.5523</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>1.5523</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.8672</v>
+        <v>-0.0208</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8356</v>
+        <v>-0.2412</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0316</v>
+        <v>0.2204</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="W18" t="n">
-        <v>1.506</v>
+        <v>1.2239</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.506</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
+          <t>K. SKUTYELNIK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.4618</v>
+        <v>-3.1915</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3368</v>
+        <v>-2.2844</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.125</v>
+        <v>-0.907</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.8789</v>
+        <v>-1.1362</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.8234</v>
+        <v>-0.3526</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0555</v>
+        <v>-0.7835</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.2144</v>
+        <v>-0.0116</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.7095</v>
+        <v>0.0824</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5049</v>
+        <v>-0.0939</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6645</v>
+        <v>-1.1246</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1139</v>
+        <v>-0.435</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5506</v>
+        <v>-0.6896</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7761</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q19" t="n">
+        <v>-1.9403</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.5821</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.6971000000000001</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.3326</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.3645</v>
+      </c>
+      <c r="V19" t="n">
         <v>0</v>
       </c>
-      <c r="R19" t="n">
-        <v>0.7761</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.5828</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.9836</v>
-      </c>
-      <c r="U19" t="n">
-        <v>-0.4008</v>
-      </c>
-      <c r="V19" t="n">
-        <v>-0.9418</v>
-      </c>
       <c r="W19" t="n">
-        <v>0.894</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. SKUTYELNIK</t>
+          <t>G. MEJÍA ACOSTA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5251</v>
+        <v>-3.8359</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4846</v>
+        <v>-1.4023</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0405</v>
+        <v>-2.4336</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1362</v>
+        <v>-3.7482</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3526</v>
+        <v>-2.0086</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7835</v>
+        <v>-1.7396</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0116</v>
+        <v>-1.0487</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0824</v>
+        <v>-0.5437</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0939</v>
+        <v>-0.5049</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1246</v>
+        <v>-2.6995</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.435</v>
+        <v>-1.4649</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6896</v>
+        <v>-1.2346</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3582</v>
+        <v>0.5821</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0.5821</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0307</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.3536</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.498</v>
+        <v>-0.3163</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. GUEYE</t>
+          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7957</v>
+        <v>-4.0835</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2603</v>
+        <v>-1.0375</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5354</v>
+        <v>-3.046</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.7257</v>
+        <v>-3.8789</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3874</v>
+        <v>-2.8234</v>
       </c>
       <c r="I21" t="n">
-        <v>-4.3383</v>
+        <v>-1.0555</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.0202</v>
+        <v>-2.2144</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8074</v>
+        <v>-1.7095</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2129</v>
+        <v>-0.5049</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.7054</v>
+        <v>-1.6645</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.58</v>
+        <v>-1.1139</v>
       </c>
       <c r="O21" t="n">
-        <v>-3.1254</v>
+        <v>-0.5506</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3881</v>
+        <v>0.7761</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3284</v>
+        <v>0.7761</v>
       </c>
       <c r="S21" t="n">
-        <v>2.1538</v>
+        <v>-0.039</v>
       </c>
       <c r="T21" t="n">
-        <v>1.7003</v>
+        <v>0.2829</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4536</v>
+        <v>-0.3219</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6119</v>
+        <v>-0.9418</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6119</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. MEJÍA ACOSTA</t>
+          <t>S. GUEYE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1607</v>
+        <v>-5.4791</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7026</v>
+        <v>-3.8619</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4581</v>
+        <v>-1.6172</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.7482</v>
+        <v>-5.7257</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.0086</v>
+        <v>-1.3874</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7396</v>
+        <v>-4.3383</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0487</v>
+        <v>-2.0202</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5437</v>
+        <v>-0.8074</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5049</v>
+        <v>-1.2129</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.6995</v>
+        <v>-3.7054</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4649</v>
+        <v>-0.58</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2346</v>
+        <v>-3.1254</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5821</v>
+        <v>0.3881</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5821</v>
+        <v>2.3284</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9946</v>
+        <v>0.4705</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6539</v>
+        <v>0.0987</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3407</v>
+        <v>0.3718</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.6119</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-22.494</v>
+        <v>-21.8267</v>
       </c>
       <c r="E23" t="n">
-        <v>2.533400000000001</v>
+        <v>2.533300000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-25.0275</v>
+        <v>-24.3599</v>
       </c>
       <c r="G23" t="n">
         <v>-25.3044</v>
@@ -2221,10 +2221,10 @@
         <v>-20.9379</v>
       </c>
       <c r="J23" t="n">
-        <v>7.387499999999999</v>
+        <v>7.3875</v>
       </c>
       <c r="K23" t="n">
-        <v>5.857799999999999</v>
+        <v>5.857799999999998</v>
       </c>
       <c r="L23" t="n">
         <v>1.5297</v>
@@ -2248,16 +2248,16 @@
         <v>15.5226</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.6955</v>
+        <v>-3.0284</v>
       </c>
       <c r="T23" t="n">
         <v>-2.4733</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2222</v>
+        <v>-0.5551</v>
       </c>
       <c r="V23" t="n">
-        <v>4.5656</v>
+        <v>4.565600000000001</v>
       </c>
       <c r="W23" t="n">
         <v>11.2015</v>
